--- a/data/GDFM 2026 Keepers.xlsx
+++ b/data/GDFM 2026 Keepers.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zachtallevast/fantasyfootball_app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9571E4-FF3F-B74B-BAF5-F2920D2F395F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4CDCE5-59CA-0242-AF1F-321D3C51FA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="600" windowWidth="13280" windowHeight="15740" xr2:uid="{79304D03-6878-D244-98D1-282091AA016A}"/>
+    <workbookView xWindow="14820" yWindow="600" windowWidth="13280" windowHeight="15740" firstSheet="1" activeTab="2" xr2:uid="{79304D03-6878-D244-98D1-282091AA016A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Team Names" sheetId="6" r:id="rId1"/>
-    <sheet name="Keepers" sheetId="1" r:id="rId2"/>
-    <sheet name="2025 Auction" sheetId="2" r:id="rId3"/>
-    <sheet name="2024 Auction" sheetId="3" r:id="rId4"/>
+    <sheet name="Team Names" sheetId="7" r:id="rId1"/>
+    <sheet name="Budget" sheetId="6" r:id="rId2"/>
+    <sheet name="Keepers" sheetId="1" r:id="rId3"/>
+    <sheet name="2025 Auction History" sheetId="2" r:id="rId4"/>
+    <sheet name="2024 Auction History" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="290">
   <si>
     <t>Owner Name</t>
   </si>
@@ -62,18 +63,6 @@
     <t>Mike</t>
   </si>
   <si>
-    <t>mike</t>
-  </si>
-  <si>
-    <t>pete</t>
-  </si>
-  <si>
-    <t>ryan</t>
-  </si>
-  <si>
-    <t>Schwabby</t>
-  </si>
-  <si>
     <t>Steve</t>
   </si>
   <si>
@@ -107,9 +96,6 @@
     <t>Sam LaPorta</t>
   </si>
   <si>
-    <t>Ernest</t>
-  </si>
-  <si>
     <t>Drake London</t>
   </si>
   <si>
@@ -134,9 +120,6 @@
     <t>Zay Flowers</t>
   </si>
   <si>
-    <t>Mike S</t>
-  </si>
-  <si>
     <t>Zach Charbonnet</t>
   </si>
   <si>
@@ -149,9 +132,6 @@
     <t>Jordan Addison</t>
   </si>
   <si>
-    <t>JK Dobbins for QJ</t>
-  </si>
-  <si>
     <t>Quinshon Judkins</t>
   </si>
   <si>
@@ -161,9 +141,6 @@
     <t>Emeka Ebuga</t>
   </si>
   <si>
-    <t>Devonta Smith</t>
-  </si>
-  <si>
     <t>RJ Harvey</t>
   </si>
   <si>
@@ -278,9 +255,6 @@
     <t>Romeo Doubs</t>
   </si>
   <si>
-    <t>QJ or Olave</t>
-  </si>
-  <si>
     <t>Cam Skattebo</t>
   </si>
   <si>
@@ -356,9 +330,6 @@
     <t>Bijan Robinson (K)</t>
   </si>
   <si>
-    <t>Bill Croskey-Merritt</t>
-  </si>
-  <si>
     <t>Bo Nix</t>
   </si>
   <si>
@@ -473,9 +444,6 @@
     <t>Derrick Henry</t>
   </si>
   <si>
-    <t>Devonta Smith (K)</t>
-  </si>
-  <si>
     <t>DJ Giddens (K)</t>
   </si>
   <si>
@@ -518,9 +486,6 @@
     <t>BRandon</t>
   </si>
   <si>
-    <t>Hollywood Brown</t>
-  </si>
-  <si>
     <t>Houston</t>
   </si>
   <si>
@@ -924,6 +889,30 @@
   </si>
   <si>
     <t xml:space="preserve">Allen S. </t>
+  </si>
+  <si>
+    <t>Jacory Croskey-Merritt-Merritt</t>
+  </si>
+  <si>
+    <t>DeVonta Smith</t>
+  </si>
+  <si>
+    <t>DeVonta Smith (K)</t>
+  </si>
+  <si>
+    <t>Marquise Brown</t>
+  </si>
+  <si>
+    <t>Stephen M.</t>
+  </si>
+  <si>
+    <t>Ryan M.</t>
+  </si>
+  <si>
+    <t>Justin S.</t>
+  </si>
+  <si>
+    <t>Jaylen H.</t>
   </si>
 </sst>
 </file>
@@ -1305,21 +1294,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2052785-6C2A-8442-9A88-119FF6B48947}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FB3726-6D79-BD4D-8AAD-A21CCA4699BA}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B1" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B2">
         <v>317</v>
@@ -1327,7 +1391,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B3">
         <v>425</v>
@@ -1335,7 +1399,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B4">
         <v>410</v>
@@ -1343,7 +1407,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B5">
         <v>430</v>
@@ -1351,7 +1415,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B6">
         <v>430</v>
@@ -1359,7 +1423,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B7">
         <v>390</v>
@@ -1367,7 +1431,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B8">
         <v>375</v>
@@ -1375,7 +1439,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B9">
         <v>431</v>
@@ -1383,7 +1447,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10">
         <v>370</v>
@@ -1391,7 +1455,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B11">
         <v>390</v>
@@ -1399,7 +1463,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B12">
         <v>365</v>
@@ -1407,7 +1471,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B13">
         <v>468</v>
@@ -1418,9 +1482,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF999445-50E4-3D40-AE7C-DE6A564E46CF}">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -1441,10 +1505,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>21</v>
@@ -1452,10 +1516,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>31</v>
@@ -1463,10 +1527,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>31</v>
@@ -1474,10 +1538,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -1485,10 +1549,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -1496,10 +1560,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -1507,10 +1571,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -1518,10 +1582,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>37</v>
@@ -1529,10 +1593,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>21</v>
@@ -1540,10 +1604,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>31</v>
@@ -1551,10 +1615,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1562,15 +1626,15 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>51</v>
@@ -1578,10 +1642,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>41</v>
@@ -1589,10 +1653,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>11</v>
@@ -1600,10 +1664,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>31</v>
@@ -1611,10 +1675,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>61</v>
@@ -1622,10 +1686,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>31</v>
@@ -1633,10 +1697,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C20">
         <v>61</v>
@@ -1644,10 +1708,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C21">
         <v>11</v>
@@ -1655,10 +1719,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>271</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>283</v>
       </c>
       <c r="C22">
         <v>51</v>
@@ -1666,10 +1730,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>11</v>
@@ -1677,10 +1741,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -1688,10 +1752,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>21</v>
@@ -1699,10 +1763,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>11</v>
@@ -1710,10 +1774,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C27">
         <v>31</v>
@@ -1721,10 +1785,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>61</v>
@@ -1732,10 +1796,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C29">
         <v>31</v>
@@ -1743,10 +1807,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C30">
         <v>51</v>
@@ -1754,10 +1818,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C31">
         <v>61</v>
@@ -1765,10 +1829,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>11</v>
@@ -1776,10 +1840,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>54</v>
@@ -1787,10 +1851,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -1798,10 +1862,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <v>16</v>
@@ -1809,10 +1873,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -1820,10 +1884,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <v>50</v>
@@ -1831,10 +1895,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C38">
         <v>11</v>
@@ -1842,10 +1906,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -1853,10 +1917,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C40">
         <v>41</v>
@@ -1864,10 +1928,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C41">
         <v>71</v>
@@ -1875,10 +1939,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1886,10 +1950,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C43">
         <v>39</v>
@@ -1897,10 +1961,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>31</v>
@@ -1908,10 +1972,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>51</v>
@@ -1919,10 +1983,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>41</v>
@@ -1930,10 +1994,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C47">
         <v>40</v>
@@ -1941,10 +2005,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C48">
         <v>11</v>
@@ -1952,10 +2016,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C49">
         <v>11</v>
@@ -1963,10 +2027,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C50">
         <v>11</v>
@@ -1974,10 +2038,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C51">
         <v>11</v>
@@ -1985,10 +2049,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C52">
         <v>11</v>
@@ -1996,10 +2060,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C53">
         <v>13</v>
@@ -2007,10 +2071,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C54">
         <v>11</v>
@@ -2018,10 +2082,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C55">
         <v>11</v>
@@ -2029,10 +2093,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C56">
         <v>11</v>
@@ -2040,10 +2104,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C57">
         <v>44</v>
@@ -2051,10 +2115,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C58">
         <v>21</v>
@@ -2062,10 +2126,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C59">
         <v>34</v>
@@ -2073,10 +2137,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>11</v>
@@ -2084,10 +2148,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C61">
         <v>11</v>
@@ -2095,10 +2159,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C62">
         <v>11</v>
@@ -2106,10 +2170,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C63">
         <v>31</v>
@@ -2117,10 +2181,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C64">
         <v>41</v>
@@ -2128,15 +2192,15 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>11</v>
@@ -2144,15 +2208,15 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C68">
         <v>11</v>
@@ -2160,10 +2224,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C69">
         <v>11</v>
@@ -2171,10 +2235,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C70">
         <v>32</v>
@@ -2182,10 +2246,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C71">
         <v>11</v>
@@ -2193,10 +2257,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C72">
         <v>11</v>
@@ -2204,23 +2268,13 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C73">
         <v>41</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B78" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2228,28 +2282,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C295444-A96B-124B-B011-7B6E61C06E9F}">
   <dimension ref="A1:C1007"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1">
         <v>61</v>
@@ -2257,10 +2311,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>12</v>
@@ -2268,10 +2322,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -2279,10 +2333,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1">
         <v>61</v>
@@ -2290,7 +2344,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -2301,10 +2355,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -2312,10 +2366,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1">
         <v>41</v>
@@ -2323,10 +2377,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1">
         <v>16</v>
@@ -2334,7 +2388,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2345,10 +2399,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1">
         <v>14</v>
@@ -2356,10 +2410,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -2367,10 +2421,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1">
         <v>31</v>
@@ -2378,10 +2432,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1">
         <v>88</v>
@@ -2389,10 +2443,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -2400,10 +2454,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1">
         <v>35</v>
@@ -2411,10 +2465,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1">
         <v>11</v>
@@ -2422,10 +2476,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1">
         <v>13</v>
@@ -2433,10 +2487,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1">
         <v>6</v>
@@ -2444,10 +2498,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1">
         <v>31</v>
@@ -2455,10 +2509,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
@@ -2466,7 +2520,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>5</v>
@@ -2477,10 +2531,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1">
         <v>11</v>
@@ -2488,10 +2542,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1">
         <v>11</v>
@@ -2499,10 +2553,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1">
         <v>11</v>
@@ -2510,7 +2564,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
@@ -2521,10 +2575,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1">
         <v>31</v>
@@ -2532,10 +2586,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -2543,10 +2597,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2554,7 +2608,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>5</v>
@@ -2565,10 +2619,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C31" s="1">
         <v>51</v>
@@ -2576,10 +2630,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1">
         <v>30</v>
@@ -2587,7 +2641,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>4</v>
@@ -2598,10 +2652,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1">
         <v>29</v>
@@ -2609,7 +2663,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>3</v>
@@ -2620,10 +2674,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="1">
         <v>7</v>
@@ -2631,7 +2685,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>3</v>
@@ -2642,10 +2696,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1">
         <v>81</v>
@@ -2653,7 +2707,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>4</v>
@@ -2664,10 +2718,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1">
         <v>7</v>
@@ -2675,10 +2729,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -2686,10 +2740,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C42" s="1">
         <v>52</v>
@@ -2697,10 +2751,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C43" s="1">
         <v>51</v>
@@ -2708,7 +2762,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>4</v>
@@ -2719,7 +2773,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>4</v>
@@ -2730,10 +2784,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1">
         <v>9</v>
@@ -2741,10 +2795,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C47" s="1">
         <v>2</v>
@@ -2752,10 +2806,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C48" s="1">
         <v>9</v>
@@ -2763,10 +2817,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C49" s="1">
         <v>100</v>
@@ -2774,10 +2828,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C50" s="1">
         <v>50</v>
@@ -2785,10 +2839,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C51" s="1">
         <v>18</v>
@@ -2796,10 +2850,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C52" s="1">
         <v>21</v>
@@ -2807,10 +2861,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C53" s="1">
         <v>44</v>
@@ -2818,10 +2872,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C54" s="1">
         <v>13</v>
@@ -2829,10 +2883,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C55" s="1">
         <v>170</v>
@@ -2840,7 +2894,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>143</v>
+        <v>284</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>5</v>
@@ -2851,10 +2905,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C57" s="1">
         <v>10</v>
@@ -2862,10 +2916,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1">
         <v>51</v>
@@ -2873,10 +2927,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C59" s="1">
         <v>49</v>
@@ -2884,10 +2938,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
@@ -2895,7 +2949,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>4</v>
@@ -2906,10 +2960,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C62" s="1">
         <v>6</v>
@@ -2917,7 +2971,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>3</v>
@@ -2928,10 +2982,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C64" s="1">
         <v>47</v>
@@ -2939,10 +2993,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
@@ -2950,10 +3004,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C66" s="1">
         <v>31</v>
@@ -2961,7 +3015,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>5</v>
@@ -2972,10 +3026,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C68" s="1">
         <v>31</v>
@@ -2983,10 +3037,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -2994,10 +3048,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>158</v>
+        <v>285</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C70" s="1">
         <v>2</v>
@@ -3005,10 +3059,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C71" s="1">
         <v>7</v>
@@ -3016,10 +3070,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C72" s="1">
         <v>2</v>
@@ -3027,10 +3081,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C73" s="1">
         <v>1</v>
@@ -3038,7 +3092,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>3</v>
@@ -3049,10 +3103,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C75" s="1">
         <v>10</v>
@@ -3060,10 +3114,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
@@ -3071,10 +3125,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C77" s="1">
         <v>80</v>
@@ -3082,10 +3136,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C78" s="1">
         <v>41</v>
@@ -3093,10 +3147,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C79" s="1">
         <v>6</v>
@@ -3104,7 +3158,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>3</v>
@@ -3115,7 +3169,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>4</v>
@@ -3126,7 +3180,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>5</v>
@@ -3137,10 +3191,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C83" s="1">
         <v>25</v>
@@ -3148,10 +3202,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C84" s="1">
         <v>39</v>
@@ -3159,7 +3213,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>5</v>
@@ -3170,10 +3224,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C86" s="1">
         <v>31</v>
@@ -3181,10 +3235,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C87" s="1">
         <v>87</v>
@@ -3192,10 +3246,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C88" s="1">
         <v>22</v>
@@ -3203,10 +3257,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C89" s="1">
         <v>34</v>
@@ -3214,7 +3268,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>3</v>
@@ -3225,10 +3279,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C91" s="1">
         <v>21</v>
@@ -3236,10 +3290,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C92" s="1">
         <v>69</v>
@@ -3247,7 +3301,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>4</v>
@@ -3258,7 +3312,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>4</v>
@@ -3269,10 +3323,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C95" s="1">
         <v>32</v>
@@ -3280,10 +3334,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C96" s="1">
         <v>22</v>
@@ -3291,10 +3345,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C97" s="1">
         <v>25</v>
@@ -3302,10 +3356,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C98" s="1">
         <v>94</v>
@@ -3313,10 +3367,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C99" s="1">
         <v>4</v>
@@ -3324,10 +3378,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C100" s="1">
         <v>32</v>
@@ -3335,10 +3389,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C101" s="1">
         <v>67</v>
@@ -3346,7 +3400,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>4</v>
@@ -3357,10 +3411,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C103" s="1">
         <v>31</v>
@@ -3368,10 +3422,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C104" s="1">
         <v>51</v>
@@ -3379,10 +3433,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C105" s="1">
         <v>3</v>
@@ -3390,10 +3444,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C106" s="1">
         <v>21</v>
@@ -3401,7 +3455,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>3</v>
@@ -3412,10 +3466,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C108" s="1">
         <v>50</v>
@@ -3423,10 +3477,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C109" s="1">
         <v>86</v>
@@ -3434,10 +3488,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C110" s="1">
         <v>61</v>
@@ -3445,10 +3499,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C111" s="1">
         <v>2</v>
@@ -3456,10 +3510,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C112" s="1">
         <v>32</v>
@@ -3467,10 +3521,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -3478,10 +3532,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C114" s="1">
         <v>25</v>
@@ -3489,7 +3543,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>5</v>
@@ -3500,7 +3554,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>5</v>
@@ -3511,10 +3565,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C117" s="1">
         <v>4</v>
@@ -3522,10 +3576,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C118" s="1">
         <v>4</v>
@@ -3533,10 +3587,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C119" s="1">
         <v>9</v>
@@ -3544,10 +3598,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C120" s="1">
         <v>31</v>
@@ -3555,7 +3609,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>3</v>
@@ -3566,7 +3620,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>4</v>
@@ -3577,10 +3631,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C123" s="1">
         <v>35</v>
@@ -3588,10 +3642,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C124" s="1">
         <v>5</v>
@@ -3599,7 +3653,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>3</v>
@@ -3610,10 +3664,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C126" s="1">
         <v>22</v>
@@ -3621,10 +3675,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C127" s="1">
         <v>22</v>
@@ -3632,7 +3686,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>5</v>
@@ -3643,10 +3697,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C129" s="1">
         <v>48</v>
@@ -3654,10 +3708,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C130" s="1">
         <v>11</v>
@@ -3665,10 +3719,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C131" s="1">
         <v>30</v>
@@ -3676,10 +3730,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C132" s="1">
         <v>11</v>
@@ -3687,10 +3741,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
@@ -3698,10 +3752,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C134" s="1">
         <v>1</v>
@@ -3709,10 +3763,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C135" s="1">
         <v>1</v>
@@ -3720,10 +3774,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C136" s="1">
         <v>35</v>
@@ -3731,10 +3785,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C137" s="1">
         <v>1</v>
@@ -3742,10 +3796,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C138" s="1">
         <v>60</v>
@@ -3753,10 +3807,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -3764,10 +3818,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C140" s="1">
         <v>20</v>
@@ -3775,10 +3829,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C141" s="1">
         <v>1</v>
@@ -3786,7 +3840,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>4</v>
@@ -3797,10 +3851,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C143" s="1">
         <v>1</v>
@@ -3808,10 +3862,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C144" s="1">
         <v>44</v>
@@ -3819,10 +3873,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C145" s="1">
         <v>1</v>
@@ -3830,7 +3884,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>5</v>
@@ -3841,10 +3895,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C147" s="1">
         <v>11</v>
@@ -3852,10 +3906,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C148" s="1">
         <v>8</v>
@@ -3863,7 +3917,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>3</v>
@@ -3874,10 +3928,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C150" s="1">
         <v>2</v>
@@ -3885,10 +3939,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C151" s="1">
         <v>22</v>
@@ -3896,10 +3950,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C152" s="1">
         <v>7</v>
@@ -3907,10 +3961,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C153" s="1">
         <v>10</v>
@@ -3918,7 +3972,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>4</v>
@@ -3929,10 +3983,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C155" s="1">
         <v>4</v>
@@ -3940,10 +3994,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C156" s="1">
         <v>26</v>
@@ -3951,7 +4005,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>5</v>
@@ -3962,10 +4016,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C158" s="1">
         <v>11</v>
@@ -3973,10 +4027,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C159" s="1">
         <v>6</v>
@@ -3984,10 +4038,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C160" s="1">
         <v>11</v>
@@ -3995,10 +4049,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C161" s="1">
         <v>24</v>
@@ -4006,7 +4060,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>3</v>
@@ -4017,7 +4071,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>3</v>
@@ -4028,7 +4082,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>5</v>
@@ -4039,10 +4093,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C165" s="1">
         <v>1</v>
@@ -4050,10 +4104,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C166" s="1">
         <v>40</v>
@@ -4061,10 +4115,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C167" s="1">
         <v>20</v>
@@ -4072,7 +4126,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>4</v>
@@ -4083,10 +4137,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C169" s="1">
         <v>1</v>
@@ -4094,10 +4148,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C170" s="1">
         <v>125</v>
@@ -4105,10 +4159,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C171" s="1">
         <v>22</v>
@@ -4116,7 +4170,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>4</v>
@@ -4127,10 +4181,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C173" s="1">
         <v>31</v>
@@ -4138,10 +4192,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C174" s="1">
         <v>40</v>
@@ -4149,7 +4203,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>4</v>
@@ -4160,7 +4214,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>3</v>
@@ -4171,10 +4225,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C177" s="1">
         <v>11</v>
@@ -4182,10 +4236,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C178" s="1">
         <v>21</v>
@@ -4193,10 +4247,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C179" s="1">
         <v>11</v>
@@ -4204,10 +4258,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C180" s="1">
         <v>3</v>
@@ -4215,7 +4269,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>4</v>
@@ -4226,10 +4280,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C182" s="1">
         <v>16</v>
@@ -4237,10 +4291,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C183" s="1">
         <v>96</v>
@@ -4248,10 +4302,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C184" s="1">
         <v>17</v>
@@ -4259,10 +4313,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C185" s="1">
         <v>1</v>
@@ -4270,7 +4324,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>4</v>
@@ -4281,7 +4335,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>3</v>
@@ -4292,7 +4346,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>3</v>
@@ -4303,10 +4357,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C189" s="1">
         <v>11</v>
@@ -4314,10 +4368,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C190" s="1">
         <v>1</v>
@@ -4325,7 +4379,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>4</v>
@@ -4336,10 +4390,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C192" s="1">
         <v>21</v>
@@ -8425,25 +8479,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D8D898-040C-9348-BE0B-A2504E20598B}">
   <dimension ref="A1:C1007"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -8454,7 +8508,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -8465,7 +8519,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -8476,7 +8530,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -8487,7 +8541,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -8498,7 +8552,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -8509,7 +8563,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -8520,7 +8574,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -8531,7 +8585,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -8542,7 +8596,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -8553,7 +8607,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
@@ -8564,7 +8618,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>3</v>
@@ -8575,7 +8629,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>3</v>
@@ -8586,7 +8640,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>3</v>
@@ -8597,7 +8651,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
@@ -8608,7 +8662,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>3</v>
@@ -8619,7 +8673,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>3</v>
@@ -8630,10 +8684,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -8641,10 +8695,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1">
         <v>32</v>
@@ -8652,10 +8706,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1">
         <v>41</v>
@@ -8663,10 +8717,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1">
         <v>25</v>
@@ -8674,10 +8728,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1">
         <v>11</v>
@@ -8685,10 +8739,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1">
         <v>51</v>
@@ -8696,10 +8750,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1">
         <v>21</v>
@@ -8707,10 +8761,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1">
         <v>61</v>
@@ -8718,10 +8772,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1">
         <v>20</v>
@@ -8729,10 +8783,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C28" s="1">
         <v>22</v>
@@ -8740,10 +8794,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1">
         <v>94</v>
@@ -8751,10 +8805,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C30" s="1">
         <v>7</v>
@@ -8762,10 +8816,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -8773,10 +8827,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1">
         <v>5</v>
@@ -8784,10 +8838,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
@@ -8795,10 +8849,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
@@ -8806,10 +8860,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
@@ -8817,7 +8871,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>4</v>
@@ -8828,7 +8882,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>4</v>
@@ -8839,7 +8893,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>4</v>
@@ -8850,7 +8904,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>4</v>
@@ -8861,7 +8915,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>4</v>
@@ -8872,7 +8926,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>4</v>
@@ -8883,7 +8937,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>4</v>
@@ -8894,7 +8948,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>4</v>
@@ -8905,7 +8959,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>4</v>
@@ -8916,7 +8970,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>4</v>
@@ -8927,7 +8981,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>4</v>
@@ -8938,7 +8992,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>4</v>
@@ -8949,7 +9003,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>4</v>
@@ -8960,7 +9014,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>4</v>
@@ -8971,7 +9025,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>4</v>
@@ -8982,7 +9036,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>4</v>
@@ -8993,7 +9047,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>4</v>
@@ -9004,7 +9058,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>4</v>
@@ -9015,7 +9069,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>5</v>
@@ -9026,7 +9080,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>5</v>
@@ -9037,7 +9091,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>5</v>
@@ -9048,7 +9102,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>143</v>
+        <v>284</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>5</v>
@@ -9059,7 +9113,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>5</v>
@@ -9070,7 +9124,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>5</v>
@@ -9081,7 +9135,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>5</v>
@@ -9092,7 +9146,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>5</v>
@@ -9103,7 +9157,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>5</v>
@@ -9114,7 +9168,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>5</v>
@@ -9125,7 +9179,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>5</v>
@@ -9136,7 +9190,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>5</v>
@@ -9147,7 +9201,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>5</v>
@@ -9158,10 +9212,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C67" s="1">
         <v>21</v>
@@ -9169,10 +9223,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C68" s="1">
         <v>41</v>
@@ -9180,10 +9234,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C69" s="1">
         <v>44</v>
@@ -9191,10 +9245,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C70" s="1">
         <v>51</v>
@@ -9202,10 +9256,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C71" s="1">
         <v>21</v>
@@ -9213,10 +9267,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C72" s="1">
         <v>51</v>
@@ -9224,10 +9278,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C73" s="1">
         <v>25</v>
@@ -9235,10 +9289,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C74" s="1">
         <v>14</v>
@@ -9246,10 +9300,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C75" s="1">
         <v>26</v>
@@ -9257,10 +9311,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C76" s="1">
         <v>10</v>
@@ -9268,10 +9322,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C77" s="1">
         <v>7</v>
@@ -9279,10 +9333,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
@@ -9290,10 +9344,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C79" s="1">
         <v>9</v>
@@ -9301,10 +9355,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C80" s="1">
         <v>4</v>
@@ -9312,10 +9366,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C81" s="1">
         <v>48</v>
@@ -9323,10 +9377,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C82" s="1">
         <v>61</v>
@@ -9334,10 +9388,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C83" s="1">
         <v>22</v>
@@ -9345,10 +9399,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C84" s="1">
         <v>31</v>
@@ -9356,10 +9410,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C85" s="1">
         <v>32</v>
@@ -9367,10 +9421,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C86" s="1">
         <v>81</v>
@@ -9378,10 +9432,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C87" s="1">
         <v>30</v>
@@ -9389,10 +9443,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C88" s="1">
         <v>8</v>
@@ -9400,10 +9454,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C89" s="1">
         <v>22</v>
@@ -9411,10 +9465,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C90" s="1">
         <v>40</v>
@@ -9422,10 +9476,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C91" s="1">
         <v>3</v>
@@ -9433,10 +9487,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C92" s="1">
         <v>4</v>
@@ -9444,10 +9498,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C93" s="1">
         <v>9</v>
@@ -9455,10 +9509,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
@@ -9466,10 +9520,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -9477,10 +9531,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
@@ -9488,10 +9542,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -9499,10 +9553,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C98" s="1">
         <v>61</v>
@@ -9510,10 +9564,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C99" s="1">
         <v>31</v>
@@ -9521,10 +9575,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C100" s="1">
         <v>22</v>
@@ -9532,10 +9586,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C101" s="1">
         <v>17</v>
@@ -9543,10 +9597,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C102" s="1">
         <v>39</v>
@@ -9554,10 +9608,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C103" s="1">
         <v>35</v>
@@ -9565,10 +9619,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C104" s="1">
         <v>49</v>
@@ -9576,10 +9630,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C105" s="1">
         <v>52</v>
@@ -9587,10 +9641,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -9598,10 +9652,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C107" s="1">
         <v>40</v>
@@ -9609,10 +9663,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -9620,10 +9674,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C109" s="1">
         <v>29</v>
@@ -9631,10 +9685,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -9642,10 +9696,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C111" s="1">
         <v>5</v>
@@ -9653,10 +9707,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C112" s="1">
         <v>4</v>
@@ -9664,10 +9718,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C113" s="1">
         <v>10</v>
@@ -9675,10 +9729,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C114" s="1">
         <v>7</v>
@@ -9686,10 +9740,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C115" s="1">
         <v>22</v>
@@ -9697,10 +9751,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C116" s="1">
         <v>30</v>
@@ -9708,10 +9762,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C117" s="1">
         <v>31</v>
@@ -9719,10 +9773,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118" s="1">
         <v>31</v>
@@ -9730,10 +9784,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C119" s="1">
         <v>31</v>
@@ -9741,10 +9795,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C120" s="1">
         <v>11</v>
@@ -9752,10 +9806,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121" s="1">
         <v>100</v>
@@ -9763,10 +9817,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C122" s="1">
         <v>11</v>
@@ -9774,10 +9828,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C123" s="1">
         <v>35</v>
@@ -9785,10 +9839,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C124" s="1">
         <v>6</v>
@@ -9796,10 +9850,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C125" s="1">
         <v>32</v>
@@ -9807,10 +9861,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C126" s="1">
         <v>47</v>
@@ -9818,10 +9872,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C127" s="1">
         <v>7</v>
@@ -9829,10 +9883,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C128" s="1">
         <v>6</v>
@@ -9840,10 +9894,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C129" s="1">
         <v>11</v>
@@ -9851,10 +9905,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C130" s="1">
         <v>31</v>
@@ -9862,10 +9916,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C131" s="1">
         <v>18</v>
@@ -9873,10 +9927,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C132" s="1">
         <v>51</v>
@@ -9884,10 +9938,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C133" s="1">
         <v>13</v>
@@ -9895,10 +9949,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1">
         <v>96</v>
@@ -9906,10 +9960,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1">
         <v>125</v>
@@ -9917,10 +9971,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C136" s="1">
         <v>86</v>
@@ -9928,10 +9982,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1">
         <v>50</v>
@@ -9939,10 +9993,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1">
         <v>3</v>
@@ -9950,10 +10004,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1">
         <v>4</v>
@@ -9961,10 +10015,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1">
         <v>3</v>
@@ -9972,10 +10026,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C141" s="1">
         <v>6</v>
@@ -9983,10 +10037,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1">
         <v>1</v>
@@ -9994,10 +10048,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C143" s="1">
         <v>12</v>
@@ -10005,10 +10059,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>158</v>
+        <v>285</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -10016,10 +10070,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C145" s="1">
         <v>1</v>
@@ -10027,10 +10081,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C146" s="1">
         <v>11</v>
@@ -10038,10 +10092,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C147" s="1">
         <v>24</v>
@@ -10049,10 +10103,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C148" s="1">
         <v>11</v>
@@ -10060,10 +10114,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C149" s="1">
         <v>16</v>
@@ -10071,10 +10125,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C150" s="1">
         <v>34</v>
@@ -10082,10 +10136,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C151" s="1">
         <v>40</v>
@@ -10093,10 +10147,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C152" s="1">
         <v>67</v>
@@ -10104,10 +10158,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C153" s="1">
         <v>50</v>
@@ -10115,10 +10169,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C154" s="1">
         <v>44</v>
@@ -10126,10 +10180,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C155" s="1">
         <v>22</v>
@@ -10137,10 +10191,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C156" s="1">
         <v>25</v>
@@ -10148,10 +10202,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C157" s="1">
         <v>5</v>
@@ -10159,10 +10213,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C158" s="1">
         <v>13</v>
@@ -10170,10 +10224,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C159" s="1">
         <v>2</v>
@@ -10181,10 +10235,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C160" s="1">
         <v>1</v>
@@ -10192,10 +10246,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C161" s="1">
         <v>11</v>
@@ -10203,10 +10257,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C162" s="1">
         <v>21</v>
@@ -10214,10 +10268,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C163" s="1">
         <v>11</v>
@@ -10225,10 +10279,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C164" s="1">
         <v>11</v>
@@ -10236,10 +10290,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C165" s="1">
         <v>31</v>
@@ -10247,10 +10301,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C166" s="1">
         <v>31</v>
@@ -10258,10 +10312,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C167" s="1">
         <v>170</v>
@@ -10269,10 +10323,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C168" s="1">
         <v>69</v>
@@ -10280,10 +10334,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C169" s="1">
         <v>31</v>
@@ -10291,10 +10345,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C170" s="1">
         <v>16</v>
@@ -10302,10 +10356,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C171" s="1">
         <v>2</v>
@@ -10313,10 +10367,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C172" s="1">
         <v>1</v>
@@ -10324,10 +10378,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C173" s="1">
         <v>2</v>
@@ -10335,10 +10389,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C174" s="1">
         <v>2</v>
@@ -10346,10 +10400,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C175" s="1">
         <v>9</v>
@@ -10357,10 +10411,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C176" s="1">
         <v>2</v>
@@ -10368,10 +10422,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C177" s="1">
         <v>11</v>
@@ -10379,10 +10433,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C178" s="1">
         <v>11</v>
@@ -10390,10 +10444,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C179" s="1">
         <v>21</v>
@@ -10401,10 +10455,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C180" s="1">
         <v>11</v>
@@ -10412,10 +10466,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C181" s="1">
         <v>10</v>
@@ -10423,10 +10477,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C182" s="1">
         <v>10</v>
@@ -10434,10 +10488,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C183" s="1">
         <v>60</v>
@@ -10445,10 +10499,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C184" s="1">
         <v>88</v>
@@ -10456,10 +10510,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C185" s="1">
         <v>80</v>
@@ -10467,10 +10521,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C186" s="1">
         <v>20</v>
@@ -10478,10 +10532,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C187" s="1">
         <v>35</v>
@@ -10489,10 +10543,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C188" s="1">
         <v>87</v>
@@ -10500,10 +10554,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C189" s="1">
         <v>1</v>
@@ -10511,10 +10565,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C190" s="1">
         <v>1</v>
@@ -10522,10 +10576,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C191" s="1">
         <v>1</v>
@@ -10533,10 +10587,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C192" s="1">
         <v>1</v>

--- a/data/GDFM 2026 Keepers.xlsx
+++ b/data/GDFM 2026 Keepers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zachtallevast/fantasyfootball_app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8F6FE0-865D-3A46-9E7C-B22037F7EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A172DEA0-3047-A945-8D98-131480733E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15500" yWindow="600" windowWidth="12600" windowHeight="15740" activeTab="1" xr2:uid="{79304D03-6878-D244-98D1-282091AA016A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Keepers" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Keepers!$A$1:$F$455</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Keepers!$A$1:$F$454</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="245">
   <si>
     <t>Keeper</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Troy</t>
   </si>
   <si>
-    <t>Womack</t>
-  </si>
-  <si>
     <t>Keon Coleman</t>
   </si>
   <si>
@@ -267,9 +264,6 @@
     <t>Baker Mayfield</t>
   </si>
   <si>
-    <t>Pete</t>
-  </si>
-  <si>
     <t>Baltimore</t>
   </si>
   <si>
@@ -654,9 +648,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
     <t>Keeper Cost</t>
   </si>
   <si>
@@ -784,6 +775,9 @@
   </si>
   <si>
     <t>Zach Charbonet</t>
+  </si>
+  <si>
+    <t>Team/Manager</t>
   </si>
 </sst>
 </file>
@@ -1179,15 +1173,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B2">
         <v>317</v>
@@ -1195,7 +1189,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B3">
         <v>425</v>
@@ -1203,7 +1197,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4">
         <v>410</v>
@@ -1211,7 +1205,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5">
         <v>430</v>
@@ -1219,7 +1213,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6">
         <v>430</v>
@@ -1227,7 +1221,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B7">
         <v>390</v>
@@ -1235,7 +1229,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B8">
         <v>375</v>
@@ -1243,7 +1237,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B9">
         <v>431</v>
@@ -1251,7 +1245,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B10">
         <v>370</v>
@@ -1259,7 +1253,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B11">
         <v>390</v>
@@ -1267,7 +1261,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B12">
         <v>365</v>
@@ -1275,7 +1269,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B13">
         <v>468</v>
@@ -1288,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD1486C-51B6-B749-A34B-52AA7241C016}">
-  <dimension ref="A1:F455"/>
+  <dimension ref="A1:F454"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
@@ -1296,33 +1290,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" t="s">
         <v>202</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>203</v>
-      </c>
-      <c r="C1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2">
         <v>2025</v>
@@ -1333,13 +1327,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3">
         <v>2025</v>
@@ -1350,13 +1344,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>2025</v>
@@ -1367,13 +1361,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D5">
         <v>61</v>
@@ -1387,13 +1381,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6">
         <v>2025</v>
@@ -1404,13 +1398,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7">
         <v>2025</v>
@@ -1421,13 +1415,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D8">
         <v>41</v>
@@ -1441,13 +1435,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="D9">
         <v>16</v>
@@ -1461,13 +1455,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10">
         <v>2025</v>
@@ -1478,13 +1472,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>196</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11">
         <v>2025</v>
@@ -1495,13 +1489,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12">
         <v>2025</v>
@@ -1512,13 +1506,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>31</v>
@@ -1532,13 +1526,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>188</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E14">
         <v>2025</v>
@@ -1549,13 +1543,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>2025</v>
@@ -1566,13 +1560,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16">
         <v>2025</v>
@@ -1583,13 +1577,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B17" t="s">
+        <v>188</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17">
         <v>11</v>
@@ -1603,13 +1597,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E18">
         <v>2025</v>
@@ -1620,13 +1614,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E19">
         <v>2025</v>
@@ -1637,13 +1631,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20">
         <v>31</v>
@@ -1657,13 +1651,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E21">
         <v>2025</v>
@@ -1674,13 +1668,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D22">
         <v>31</v>
@@ -1694,13 +1688,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -1714,13 +1708,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D24">
         <v>11</v>
@@ -1734,13 +1728,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>11</v>
@@ -1754,13 +1748,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E26">
         <v>2025</v>
@@ -1771,13 +1765,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D27">
         <v>31</v>
@@ -1791,13 +1785,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28">
         <v>2025</v>
@@ -1808,13 +1802,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E29">
         <v>2025</v>
@@ -1825,13 +1819,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E30">
         <v>2025</v>
@@ -1842,13 +1836,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B31" t="s">
+        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -1862,13 +1856,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32">
         <v>30</v>
@@ -1882,13 +1876,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E33">
         <v>2025</v>
@@ -1899,13 +1893,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E34">
         <v>2025</v>
@@ -1916,13 +1910,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>31</v>
@@ -1936,13 +1930,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>2025</v>
@@ -1953,13 +1947,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E37">
         <v>2025</v>
@@ -1970,13 +1964,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D38">
         <v>81</v>
@@ -1990,13 +1984,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D39">
         <v>27</v>
@@ -2010,13 +2004,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>207</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>196</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>2025</v>
@@ -2027,13 +2021,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41">
         <v>2025</v>
@@ -2044,13 +2038,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E42">
         <v>2025</v>
@@ -2061,13 +2055,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -2081,13 +2075,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E44">
         <v>2025</v>
@@ -2098,13 +2092,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E45">
         <v>2025</v>
@@ -2115,13 +2109,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E46">
         <v>2025</v>
@@ -2132,13 +2126,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E47">
         <v>2025</v>
@@ -2149,13 +2143,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>207</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B48" t="s">
+        <v>196</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E48">
         <v>2025</v>
@@ -2166,13 +2160,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E49">
         <v>2025</v>
@@ -2183,13 +2177,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E50">
         <v>2025</v>
@@ -2200,13 +2194,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D51">
         <v>18</v>
@@ -2220,13 +2214,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B52" t="s">
+        <v>196</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D52">
         <v>21</v>
@@ -2240,13 +2234,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E53">
         <v>2025</v>
@@ -2257,13 +2251,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E54">
         <v>2025</v>
@@ -2274,13 +2268,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E55">
         <v>2025</v>
@@ -2291,13 +2285,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D56">
         <v>41</v>
@@ -2311,13 +2305,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>207</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B57" t="s">
+        <v>188</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D57">
         <v>10</v>
@@ -2331,13 +2325,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D58">
         <v>51</v>
@@ -2351,13 +2345,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E59">
         <v>2025</v>
@@ -2368,13 +2362,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E60">
         <v>2025</v>
@@ -2385,13 +2379,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B61" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61">
         <v>31</v>
@@ -2405,13 +2399,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E62">
         <v>2025</v>
@@ -2422,13 +2416,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E63">
         <v>2025</v>
@@ -2439,13 +2433,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E64">
         <v>2025</v>
@@ -2456,13 +2450,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>207</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B65" t="s">
+        <v>188</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E65">
         <v>2025</v>
@@ -2473,13 +2467,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B66" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D66">
         <v>31</v>
@@ -2493,13 +2487,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D67">
         <v>100</v>
@@ -2513,13 +2507,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D68">
         <v>31</v>
@@ -2533,13 +2527,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E69">
         <v>2025</v>
@@ -2550,13 +2544,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E70">
         <v>2025</v>
@@ -2567,13 +2561,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E71">
         <v>2025</v>
@@ -2584,13 +2578,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B72" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E72">
         <v>2025</v>
@@ -2601,13 +2595,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B73" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>2025</v>
@@ -2618,13 +2612,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B74" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E74">
         <v>2025</v>
@@ -2635,13 +2629,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>207</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B75" t="s">
+        <v>188</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D75">
         <v>10</v>
@@ -2655,13 +2649,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>207</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B76" t="s">
+        <v>188</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E76">
         <v>2025</v>
@@ -2672,13 +2666,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>207</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B77" t="s">
+        <v>188</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E77">
         <v>2025</v>
@@ -2689,13 +2683,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>207</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B78" t="s">
+        <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D78">
         <v>41</v>
@@ -2709,13 +2703,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E79">
         <v>2025</v>
@@ -2726,13 +2720,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D80">
         <v>21</v>
@@ -2746,13 +2740,13 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E81">
         <v>2025</v>
@@ -2763,13 +2757,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E82">
         <v>2025</v>
@@ -2780,13 +2774,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D83">
         <v>25</v>
@@ -2800,13 +2794,13 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E84">
         <v>2025</v>
@@ -2817,13 +2811,13 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D85">
         <v>42</v>
@@ -2837,13 +2831,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D86">
         <v>31</v>
@@ -2857,13 +2851,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>207</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B87" t="s">
+        <v>188</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E87">
         <v>2025</v>
@@ -2874,13 +2868,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E88">
         <v>2025</v>
@@ -2891,13 +2885,13 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E89">
         <v>2025</v>
@@ -2908,13 +2902,13 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E90">
         <v>2025</v>
@@ -2925,13 +2919,13 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>207</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B91" t="s">
+        <v>188</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D91">
         <v>21</v>
@@ -2945,13 +2939,13 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E92">
         <v>2025</v>
@@ -2962,13 +2956,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E93">
         <v>2025</v>
@@ -2979,13 +2973,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D94">
         <v>41</v>
@@ -2999,13 +2993,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D95">
         <v>32</v>
@@ -3019,13 +3013,13 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E96">
         <v>2025</v>
@@ -3036,13 +3030,13 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>207</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B97" t="s">
+        <v>196</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E97">
         <v>2025</v>
@@ -3053,13 +3047,13 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E98">
         <v>2025</v>
@@ -3070,13 +3064,13 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E99">
         <v>2025</v>
@@ -3087,13 +3081,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D100">
         <v>32</v>
@@ -3107,13 +3101,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E101">
         <v>2025</v>
@@ -3124,13 +3118,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B102" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E102">
         <v>2025</v>
@@ -3141,13 +3135,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E103">
         <v>2025</v>
@@ -3158,13 +3152,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>207</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B104" t="s">
+        <v>196</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D104">
         <v>51</v>
@@ -3178,13 +3172,13 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B105" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E105">
         <v>2025</v>
@@ -3195,13 +3189,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D106">
         <v>21</v>
@@ -3215,13 +3209,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E107">
         <v>2025</v>
@@ -3232,13 +3226,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B108" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E108">
         <v>2025</v>
@@ -3249,13 +3243,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E109">
         <v>2025</v>
@@ -3266,13 +3260,13 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B110" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D110">
         <v>61</v>
@@ -3286,13 +3280,13 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E111">
         <v>2025</v>
@@ -3303,13 +3297,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B112" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E112">
         <v>2025</v>
@@ -3320,13 +3314,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B113" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E113">
         <v>2025</v>
@@ -3337,13 +3331,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B114" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E114">
         <v>2025</v>
@@ -3354,13 +3348,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D115">
         <v>51</v>
@@ -3374,13 +3368,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E116">
         <v>2025</v>
@@ -3391,13 +3385,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>207</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B117" t="s">
+        <v>196</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E117">
         <v>2025</v>
@@ -3408,13 +3402,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E118">
         <v>2025</v>
@@ -3425,13 +3419,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B119" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E119">
         <v>2025</v>
@@ -3442,13 +3436,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B120" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D120">
         <v>31</v>
@@ -3462,13 +3456,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B121" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>11</v>
@@ -3482,13 +3476,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B122" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E122">
         <v>2025</v>
@@ -3499,13 +3493,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>207</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B123" t="s">
+        <v>188</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E123">
         <v>2025</v>
@@ -3516,13 +3510,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B124" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E124">
         <v>2025</v>
@@ -3533,13 +3527,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B125" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E125">
         <v>2025</v>
@@ -3550,13 +3544,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B126" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D126">
         <v>22</v>
@@ -3570,13 +3564,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D127">
         <v>22</v>
@@ -3590,13 +3584,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B128" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D128">
         <v>11</v>
@@ -3610,13 +3604,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B129" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D129">
         <v>48</v>
@@ -3630,13 +3624,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B130" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D130">
         <v>11</v>
@@ -3650,13 +3644,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B131" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E131">
         <v>2025</v>
@@ -3667,13 +3661,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D132">
         <v>11</v>
@@ -3687,13 +3681,13 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E133">
         <v>2025</v>
@@ -3704,13 +3698,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>207</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B134" t="s">
+        <v>188</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E134">
         <v>2025</v>
@@ -3721,13 +3715,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B135" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E135">
         <v>2025</v>
@@ -3738,13 +3732,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B136" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E136">
         <v>2025</v>
@@ -3755,13 +3749,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B137" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>2025</v>
@@ -3772,13 +3766,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>207</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B138" t="s">
+        <v>188</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E138">
         <v>2025</v>
@@ -3789,13 +3783,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B139" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E139">
         <v>2025</v>
@@ -3806,13 +3800,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>207</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B140" t="s">
+        <v>188</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E140">
         <v>2025</v>
@@ -3823,13 +3817,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E141">
         <v>2025</v>
@@ -3840,13 +3834,13 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B142" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E142">
         <v>2025</v>
@@ -3857,13 +3851,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B143" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>2025</v>
@@ -3874,13 +3868,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>207</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B144" t="s">
+        <v>196</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D144">
         <v>44</v>
@@ -3894,13 +3888,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B145" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E145">
         <v>2025</v>
@@ -3911,13 +3905,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B146" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E146">
         <v>2025</v>
@@ -3928,13 +3922,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B147" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E147">
         <v>2025</v>
@@ -3945,13 +3939,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B148" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E148">
         <v>2025</v>
@@ -3962,13 +3956,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B149" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D149">
         <v>21</v>
@@ -3982,13 +3976,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E150">
         <v>2025</v>
@@ -3999,13 +3993,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B151" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E151">
         <v>2025</v>
@@ -4016,13 +4010,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B152" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E152">
         <v>2025</v>
@@ -4033,13 +4027,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>207</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B153" t="s">
+        <v>196</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E153">
         <v>2025</v>
@@ -4050,13 +4044,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B154" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D154">
         <v>21</v>
@@ -4070,13 +4064,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B155" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E155">
         <v>2025</v>
@@ -4087,13 +4081,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>207</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B156" t="s">
+        <v>196</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E156">
         <v>2025</v>
@@ -4104,13 +4098,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E157">
         <v>2025</v>
@@ -4121,13 +4115,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>207</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B158" t="s">
+        <v>188</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D158">
         <v>11</v>
@@ -4141,13 +4135,13 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B159" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E159">
         <v>2025</v>
@@ -4158,13 +4152,13 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D160">
         <v>11</v>
@@ -4178,13 +4172,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B161" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D161">
         <v>24</v>
@@ -4198,13 +4192,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B162" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D162">
         <v>21</v>
@@ -4218,13 +4212,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B163" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D163">
         <v>71</v>
@@ -4238,13 +4232,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B164" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E164">
         <v>2025</v>
@@ -4255,13 +4249,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>207</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B165" t="s">
+        <v>188</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E165">
         <v>2025</v>
@@ -4272,13 +4266,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B166" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E166">
         <v>2025</v>
@@ -4289,13 +4283,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B167" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E167">
         <v>2025</v>
@@ -4306,13 +4300,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B168" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D168">
         <v>51</v>
@@ -4326,13 +4320,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>207</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B169" t="s">
+        <v>196</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E169">
         <v>2025</v>
@@ -4343,13 +4337,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B170" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E170">
         <v>2025</v>
@@ -4360,13 +4354,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B171" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D171">
         <v>22</v>
@@ -4380,13 +4374,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B172" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E172">
         <v>2025</v>
@@ -4397,13 +4391,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D173">
         <v>31</v>
@@ -4417,13 +4411,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B174" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E174">
         <v>2025</v>
@@ -4434,13 +4428,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B175" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E175">
         <v>2025</v>
@@ -4451,13 +4445,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E176">
         <v>2025</v>
@@ -4468,13 +4462,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B177" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D177">
         <v>11</v>
@@ -4488,13 +4482,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>207</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B178" t="s">
+        <v>196</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D178">
         <v>21</v>
@@ -4508,13 +4502,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>207</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B179" t="s">
+        <v>188</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D179">
         <v>11</v>
@@ -4528,13 +4522,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B180" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E180">
         <v>2025</v>
@@ -4545,13 +4539,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B181" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E181">
         <v>2025</v>
@@ -4562,13 +4556,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E182">
         <v>2025</v>
@@ -4579,13 +4573,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B183" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E183">
         <v>2025</v>
@@ -4596,13 +4590,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B184" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D184">
         <v>17</v>
@@ -4616,13 +4610,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B185" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E185">
         <v>2025</v>
@@ -4633,13 +4627,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B186" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E186">
         <v>2025</v>
@@ -4650,13 +4644,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E187">
         <v>2025</v>
@@ -4667,13 +4661,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E188">
         <v>2025</v>
@@ -4684,13 +4678,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D189">
         <v>11</v>
@@ -4704,13 +4698,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E190">
         <v>2025</v>
@@ -4721,13 +4715,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B191" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D191">
         <v>21</v>
@@ -4741,13 +4735,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D192">
         <v>21</v>
@@ -4761,13 +4755,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B193" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D193">
         <v>11</v>
@@ -4781,13 +4775,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D194">
         <v>21</v>
@@ -4801,13 +4795,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B195" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D195">
         <v>21</v>
@@ -4821,13 +4815,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B196" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D196">
         <v>31</v>
@@ -4841,13 +4835,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B197" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D197">
         <v>71</v>
@@ -4861,13 +4855,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B198" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D198">
         <v>21</v>
@@ -4881,13 +4875,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E199">
         <v>2024</v>
@@ -4898,13 +4892,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B200" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E200">
         <v>2024</v>
@@ -4915,13 +4909,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E201">
         <v>2024</v>
@@ -4932,13 +4926,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B202" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E202">
         <v>2024</v>
@@ -4949,13 +4943,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B203" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E203">
         <v>2024</v>
@@ -4966,13 +4960,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E204">
         <v>2024</v>
@@ -4983,13 +4977,13 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E205">
         <v>2024</v>
@@ -5000,13 +4994,13 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E206">
         <v>2024</v>
@@ -5017,13 +5011,13 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B207" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E207">
         <v>2024</v>
@@ -5034,13 +5028,13 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B208" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E208">
         <v>2024</v>
@@ -5051,13 +5045,13 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B209" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E209">
         <v>2024</v>
@@ -5068,13 +5062,13 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B210" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E210">
         <v>2024</v>
@@ -5085,13 +5079,13 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B211" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D211">
         <v>32</v>
@@ -5105,13 +5099,13 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B212" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D212">
         <v>41</v>
@@ -5125,13 +5119,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B213" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D213">
         <v>25</v>
@@ -5145,13 +5139,13 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B214" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D214">
         <v>11</v>
@@ -5165,13 +5159,13 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B215" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -5185,13 +5179,13 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B216" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D216">
         <v>21</v>
@@ -5205,13 +5199,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B217" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E217">
         <v>2024</v>
@@ -5222,13 +5216,13 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B218" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E218">
         <v>2024</v>
@@ -5239,13 +5233,13 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B219" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E219">
         <v>2024</v>
@@ -5256,13 +5250,13 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B220" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E220">
         <v>2024</v>
@@ -5273,13 +5267,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B221" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E221">
         <v>2024</v>
@@ -5290,13 +5284,13 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B222" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E222">
         <v>2024</v>
@@ -5307,13 +5301,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B223" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E223">
         <v>2024</v>
@@ -5324,13 +5318,13 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B224" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E224">
         <v>2024</v>
@@ -5341,13 +5335,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B225" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E225">
         <v>2024</v>
@@ -5358,13 +5352,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B226" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E226">
         <v>2024</v>
@@ -5375,13 +5369,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B227" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D227">
         <v>21</v>
@@ -5395,13 +5389,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B228" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D228">
         <v>21</v>
@@ -5415,13 +5409,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B229" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D229">
         <v>31</v>
@@ -5435,13 +5429,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B230" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D230">
         <v>51</v>
@@ -5455,13 +5449,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B231" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D231">
         <v>41</v>
@@ -5475,13 +5469,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B232" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D232">
         <v>27</v>
@@ -5495,13 +5489,13 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B233" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E233">
         <v>2024</v>
@@ -5512,13 +5506,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B234" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E234">
         <v>2024</v>
@@ -5529,13 +5523,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B235" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E235">
         <v>2024</v>
@@ -5546,13 +5540,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B236" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E236">
         <v>2024</v>
@@ -5563,13 +5557,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B237" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E237">
         <v>2024</v>
@@ -5580,13 +5574,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B238" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E238">
         <v>2024</v>
@@ -5597,13 +5591,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B239" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E239">
         <v>2024</v>
@@ -5614,13 +5608,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B240" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E240">
         <v>2024</v>
@@ -5631,13 +5625,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B241" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -5648,13 +5642,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B242" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E242">
         <v>2024</v>
@@ -5665,13 +5659,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B243" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E243">
         <v>2024</v>
@@ -5682,13 +5676,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B244" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E244">
         <v>2024</v>
@@ -5699,13 +5693,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B245" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D245">
         <v>11</v>
@@ -5719,13 +5713,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B246" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D246">
         <v>51</v>
@@ -5739,13 +5733,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B247" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D247">
         <v>100</v>
@@ -5759,13 +5753,13 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B248" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D248">
         <v>41</v>
@@ -5779,13 +5773,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B249" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D249">
         <v>42</v>
@@ -5799,13 +5793,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B250" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D250">
         <v>31</v>
@@ -5819,13 +5813,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B251" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E251">
         <v>2024</v>
@@ -5836,13 +5830,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B252" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E252">
         <v>2024</v>
@@ -5853,13 +5847,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B253" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E253">
         <v>2024</v>
@@ -5870,13 +5864,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B254" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E254">
         <v>2024</v>
@@ -5887,13 +5881,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B255" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E255">
         <v>2024</v>
@@ -5904,13 +5898,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B256" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E256">
         <v>2024</v>
@@ -5921,13 +5915,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B257" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E257">
         <v>2024</v>
@@ -5938,13 +5932,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>207</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B258" t="s">
+        <v>196</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D258">
         <v>21</v>
@@ -5958,13 +5952,13 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>207</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B259" t="s">
+        <v>196</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D259">
         <v>41</v>
@@ -5978,13 +5972,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>207</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B260" t="s">
+        <v>196</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D260">
         <v>44</v>
@@ -5998,13 +5992,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>207</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B261" t="s">
+        <v>196</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D261">
         <v>51</v>
@@ -6018,13 +6012,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>207</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B262" t="s">
+        <v>196</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D262">
         <v>21</v>
@@ -6038,13 +6032,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>207</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B263" t="s">
+        <v>196</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D263">
         <v>51</v>
@@ -6058,13 +6052,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>207</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B264" t="s">
+        <v>196</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E264">
         <v>2024</v>
@@ -6075,13 +6069,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>207</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B265" t="s">
+        <v>196</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -6092,13 +6086,13 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>207</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B266" t="s">
+        <v>196</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E266">
         <v>2024</v>
@@ -6109,13 +6103,13 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>207</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B267" t="s">
+        <v>196</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E267">
         <v>2024</v>
@@ -6126,13 +6120,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>207</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B268" t="s">
+        <v>196</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E268">
         <v>2024</v>
@@ -6143,13 +6137,13 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>207</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B269" t="s">
+        <v>196</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E269">
         <v>2024</v>
@@ -6160,13 +6154,13 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>207</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B270" t="s">
+        <v>196</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E270">
         <v>2024</v>
@@ -6177,13 +6171,13 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>207</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>74</v>
+        <v>204</v>
+      </c>
+      <c r="B271" t="s">
+        <v>196</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E271">
         <v>2024</v>
@@ -6194,13 +6188,13 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B272" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D272">
         <v>48</v>
@@ -6214,13 +6208,13 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B273" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D273">
         <v>61</v>
@@ -6234,13 +6228,13 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B274" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D274">
         <v>22</v>
@@ -6254,13 +6248,13 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B275" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D275">
         <v>31</v>
@@ -6274,13 +6268,13 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B276" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D276">
         <v>32</v>
@@ -6294,13 +6288,13 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B277" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D277">
         <v>81</v>
@@ -6314,13 +6308,13 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B278" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E278">
         <v>2024</v>
@@ -6331,13 +6325,13 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B279" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E279">
         <v>2024</v>
@@ -6348,13 +6342,13 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B280" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E280">
         <v>2024</v>
@@ -6365,13 +6359,13 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B281" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E281">
         <v>2024</v>
@@ -6382,13 +6376,13 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B282" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E282">
         <v>2024</v>
@@ -6399,13 +6393,13 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B283" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E283">
         <v>2024</v>
@@ -6416,13 +6410,13 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B284" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E284">
         <v>2024</v>
@@ -6433,13 +6427,13 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B285" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E285">
         <v>2024</v>
@@ -6450,13 +6444,13 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B286" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E286">
         <v>2024</v>
@@ -6467,13 +6461,13 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B287" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E287">
         <v>2024</v>
@@ -6484,13 +6478,13 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B288" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E288">
         <v>2024</v>
@@ -6501,13 +6495,13 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B289" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D289">
         <v>61</v>
@@ -6521,13 +6515,13 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B290" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D290">
         <v>31</v>
@@ -6541,13 +6535,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B291" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D291">
         <v>22</v>
@@ -6561,13 +6555,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B292" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D292">
         <v>17</v>
@@ -6581,13 +6575,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B293" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E293">
         <v>2024</v>
@@ -6598,13 +6592,13 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B294" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E294">
         <v>2024</v>
@@ -6615,13 +6609,13 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B295" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E295">
         <v>2024</v>
@@ -6632,13 +6626,13 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B296" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E296">
         <v>2024</v>
@@ -6649,13 +6643,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B297" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E297">
         <v>2024</v>
@@ -6666,13 +6660,13 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B298" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E298">
         <v>2024</v>
@@ -6683,13 +6677,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B299" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E299">
         <v>2024</v>
@@ -6700,13 +6694,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B300" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E300">
         <v>2024</v>
@@ -6717,13 +6711,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B301" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E301">
         <v>2024</v>
@@ -6734,13 +6728,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B302" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E302">
         <v>2024</v>
@@ -6751,13 +6745,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B303" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E303">
         <v>2024</v>
@@ -6768,13 +6762,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B304" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E304">
         <v>2024</v>
@@ -6785,13 +6779,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B305" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E305">
         <v>2024</v>
@@ -6802,13 +6796,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B306" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D306">
         <v>22</v>
@@ -6822,13 +6816,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B307" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D307">
         <v>30</v>
@@ -6842,13 +6836,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B308" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D308">
         <v>31</v>
@@ -6862,13 +6856,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B309" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D309">
         <v>31</v>
@@ -6882,13 +6876,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B310" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D310">
         <v>31</v>
@@ -6902,13 +6896,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B311" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D311">
         <v>11</v>
@@ -6922,13 +6916,13 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B312" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E312">
         <v>2024</v>
@@ -6939,13 +6933,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B313" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E313">
         <v>2024</v>
@@ -6956,13 +6950,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B314" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E314">
         <v>2024</v>
@@ -6973,13 +6967,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B315" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E315">
         <v>2024</v>
@@ -6990,13 +6984,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B316" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E316">
         <v>2024</v>
@@ -7007,13 +7001,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B317" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E317">
         <v>2024</v>
@@ -7024,13 +7018,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B318" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E318">
         <v>2024</v>
@@ -7041,13 +7035,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B319" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E319">
         <v>2024</v>
@@ -7058,13 +7052,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B320" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D320">
         <v>11</v>
@@ -7078,13 +7072,13 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B321" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D321">
         <v>31</v>
@@ -7098,13 +7092,13 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B322" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D322">
         <v>18</v>
@@ -7118,13 +7112,13 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B323" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D323">
         <v>51</v>
@@ -7138,13 +7132,13 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B324" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E324">
         <v>2024</v>
@@ -7155,13 +7149,13 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B325" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E325">
         <v>2024</v>
@@ -7172,13 +7166,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B326" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E326">
         <v>2024</v>
@@ -7189,13 +7183,13 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B327" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E327">
         <v>2024</v>
@@ -7206,13 +7200,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B328" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E328">
         <v>2024</v>
@@ -7223,13 +7217,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B329" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E329">
         <v>2024</v>
@@ -7240,13 +7234,13 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B330" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E330">
         <v>2024</v>
@@ -7257,13 +7251,13 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B331" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E331">
         <v>2024</v>
@@ -7274,13 +7268,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B332" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E332">
         <v>2024</v>
@@ -7291,13 +7285,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B333" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E333">
         <v>2024</v>
@@ -7308,13 +7302,13 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B334" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E334">
         <v>2024</v>
@@ -7325,13 +7319,13 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B335" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E335">
         <v>2024</v>
@@ -7342,13 +7336,13 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B336" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E336">
         <v>2024</v>
@@ -7359,13 +7353,13 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B337" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D337">
         <v>11</v>
@@ -7379,13 +7373,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B338" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D338">
         <v>24</v>
@@ -7399,13 +7393,13 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B339" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D339">
         <v>11</v>
@@ -7419,13 +7413,13 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
+        <v>204</v>
+      </c>
+      <c r="B340" t="s">
+        <v>187</v>
+      </c>
+      <c r="C340" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B340" t="s">
-        <v>189</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="D340">
         <v>16</v>
@@ -7439,13 +7433,13 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B341" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E341">
         <v>2024</v>
@@ -7456,13 +7450,13 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B342" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E342">
         <v>2024</v>
@@ -7473,13 +7467,13 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B343" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E343">
         <v>2024</v>
@@ -7490,13 +7484,13 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B344" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E344">
         <v>2024</v>
@@ -7507,13 +7501,13 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B345" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E345">
         <v>2024</v>
@@ -7524,13 +7518,13 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B346" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E346">
         <v>2024</v>
@@ -7541,13 +7535,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B347" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E347">
         <v>2024</v>
@@ -7558,13 +7552,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B348" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E348">
         <v>2024</v>
@@ -7575,13 +7569,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B349" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E349">
         <v>2024</v>
@@ -7592,13 +7586,13 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B350" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E350">
         <v>2024</v>
@@ -7609,13 +7603,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B351" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E351">
         <v>2024</v>
@@ -7626,13 +7620,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D352">
         <v>11</v>
@@ -7646,13 +7640,13 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D353">
         <v>21</v>
@@ -7666,13 +7660,13 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D354">
         <v>11</v>
@@ -7686,13 +7680,13 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D355">
         <v>11</v>
@@ -7706,13 +7700,13 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D356">
         <v>31</v>
@@ -7726,13 +7720,13 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D357">
         <v>31</v>
@@ -7746,13 +7740,13 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E358">
         <v>2024</v>
@@ -7763,13 +7757,13 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E359">
         <v>2024</v>
@@ -7780,13 +7774,13 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E360">
         <v>2024</v>
@@ -7797,13 +7791,13 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E361">
         <v>2024</v>
@@ -7814,13 +7808,13 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E362">
         <v>2024</v>
@@ -7831,13 +7825,13 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E363">
         <v>2024</v>
@@ -7848,13 +7842,13 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E364">
         <v>2024</v>
@@ -7865,13 +7859,13 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E365">
         <v>2024</v>
@@ -7882,13 +7876,13 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E366">
         <v>2024</v>
@@ -7899,13 +7893,13 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E367">
         <v>2024</v>
@@ -7916,13 +7910,13 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>207</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B368" t="s">
+        <v>188</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D368">
         <v>11</v>
@@ -7936,13 +7930,13 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>207</v>
-      </c>
-      <c r="B369" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B369" t="s">
+        <v>188</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D369">
         <v>11</v>
@@ -7956,13 +7950,13 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>207</v>
-      </c>
-      <c r="B370" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B370" t="s">
+        <v>188</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D370">
         <v>21</v>
@@ -7976,13 +7970,13 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>207</v>
-      </c>
-      <c r="B371" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B371" t="s">
+        <v>188</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D371">
         <v>11</v>
@@ -7996,13 +7990,13 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>207</v>
-      </c>
-      <c r="B372" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B372" t="s">
+        <v>188</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D372">
         <v>10</v>
@@ -8016,13 +8010,13 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>207</v>
-      </c>
-      <c r="B373" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B373" t="s">
+        <v>188</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D373">
         <v>10</v>
@@ -8036,13 +8030,13 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>207</v>
-      </c>
-      <c r="B374" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B374" t="s">
+        <v>188</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E374">
         <v>2024</v>
@@ -8053,13 +8047,13 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>207</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B375" t="s">
+        <v>188</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E375">
         <v>2024</v>
@@ -8070,13 +8064,13 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>207</v>
-      </c>
-      <c r="B376" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B376" t="s">
+        <v>188</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E376">
         <v>2024</v>
@@ -8087,13 +8081,13 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>207</v>
-      </c>
-      <c r="B377" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B377" t="s">
+        <v>188</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E377">
         <v>2024</v>
@@ -8104,13 +8098,13 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>207</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B378" t="s">
+        <v>188</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E378">
         <v>2024</v>
@@ -8121,13 +8115,13 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>207</v>
-      </c>
-      <c r="B379" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B379" t="s">
+        <v>188</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E379">
         <v>2024</v>
@@ -8138,13 +8132,13 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>207</v>
-      </c>
-      <c r="B380" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B380" t="s">
+        <v>188</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E380">
         <v>2024</v>
@@ -8155,13 +8149,13 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>207</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B381" t="s">
+        <v>188</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E381">
         <v>2024</v>
@@ -8172,13 +8166,13 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>207</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B382" t="s">
+        <v>188</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E382">
         <v>2024</v>
@@ -8189,13 +8183,13 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>207</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+      <c r="B383" t="s">
+        <v>188</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E383">
         <v>2024</v>
@@ -8209,10 +8203,10 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D384">
         <v>21</v>
@@ -8226,10 +8220,10 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D385">
         <v>31</v>
@@ -8243,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D386">
         <v>31</v>
@@ -8260,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D387">
         <v>11</v>
@@ -8277,10 +8271,10 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D388">
         <v>41</v>
@@ -8294,10 +8288,10 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D389">
         <v>31</v>
@@ -8311,10 +8305,10 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C390" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D390">
         <v>40</v>
@@ -8328,10 +8322,10 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C391" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D391">
         <v>37</v>
@@ -8345,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C392" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D392">
         <v>21</v>
@@ -8362,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C393" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D393">
         <v>31</v>
@@ -8379,10 +8373,10 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C394" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D394">
         <v>11</v>
@@ -8396,7 +8390,13 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>190</v>
+        <v>199</v>
+      </c>
+      <c r="C395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395">
+        <v>51</v>
       </c>
       <c r="E395">
         <v>2026</v>
@@ -8407,13 +8407,13 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C396" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D396">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E396">
         <v>2026</v>
@@ -8424,13 +8424,13 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C397" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D397">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="E397">
         <v>2026</v>
@@ -8441,13 +8441,13 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C398" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D398">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E398">
         <v>2026</v>
@@ -8458,13 +8458,13 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C399" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D399">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E399">
         <v>2026</v>
@@ -8475,13 +8475,13 @@
         <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C400" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D400">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E400">
         <v>2026</v>
@@ -8492,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C401" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D401">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E401">
         <v>2026</v>
@@ -8509,13 +8509,13 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C402" t="s">
         <v>22</v>
       </c>
       <c r="D402">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="E402">
         <v>2026</v>
@@ -8526,13 +8526,13 @@
         <v>0</v>
       </c>
       <c r="B403" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C403" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="D403">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E403">
         <v>2026</v>
@@ -8543,13 +8543,13 @@
         <v>0</v>
       </c>
       <c r="B404" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C404" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="D404">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E404">
         <v>2026</v>
@@ -8560,13 +8560,13 @@
         <v>0</v>
       </c>
       <c r="B405" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C405" t="s">
         <v>24</v>
       </c>
       <c r="D405">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E405">
         <v>2026</v>
@@ -8577,13 +8577,13 @@
         <v>0</v>
       </c>
       <c r="B406" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C406" t="s">
         <v>25</v>
       </c>
       <c r="D406">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E406">
         <v>2026</v>
@@ -8594,13 +8594,13 @@
         <v>0</v>
       </c>
       <c r="B407" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C407" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D407">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E407">
         <v>2026</v>
@@ -8611,13 +8611,13 @@
         <v>0</v>
       </c>
       <c r="B408" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C408" t="s">
         <v>34</v>
       </c>
       <c r="D408">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E408">
         <v>2026</v>
@@ -8628,13 +8628,13 @@
         <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C409" t="s">
         <v>35</v>
       </c>
       <c r="D409">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E409">
         <v>2026</v>
@@ -8645,13 +8645,13 @@
         <v>0</v>
       </c>
       <c r="B410" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C410" t="s">
         <v>36</v>
       </c>
       <c r="D410">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E410">
         <v>2026</v>
@@ -8662,13 +8662,13 @@
         <v>0</v>
       </c>
       <c r="B411" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C411" t="s">
         <v>37</v>
       </c>
       <c r="D411">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E411">
         <v>2026</v>
@@ -8679,13 +8679,13 @@
         <v>0</v>
       </c>
       <c r="B412" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C412" t="s">
         <v>38</v>
       </c>
       <c r="D412">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E412">
         <v>2026</v>
@@ -8696,13 +8696,13 @@
         <v>0</v>
       </c>
       <c r="B413" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C413" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D413">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="E413">
         <v>2026</v>
@@ -8713,13 +8713,13 @@
         <v>0</v>
       </c>
       <c r="B414" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C414" t="s">
         <v>28</v>
       </c>
       <c r="D414">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E414">
         <v>2026</v>
@@ -8730,13 +8730,13 @@
         <v>0</v>
       </c>
       <c r="B415" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C415" t="s">
         <v>29</v>
       </c>
       <c r="D415">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="E415">
         <v>2026</v>
@@ -8747,13 +8747,13 @@
         <v>0</v>
       </c>
       <c r="B416" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C416" t="s">
         <v>30</v>
       </c>
       <c r="D416">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E416">
         <v>2026</v>
@@ -8764,13 +8764,13 @@
         <v>0</v>
       </c>
       <c r="B417" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C417" t="s">
         <v>31</v>
       </c>
       <c r="D417">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E417">
         <v>2026</v>
@@ -8781,13 +8781,13 @@
         <v>0</v>
       </c>
       <c r="B418" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C418" t="s">
         <v>32</v>
       </c>
       <c r="D418">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E418">
         <v>2026</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="B419" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C419" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D419">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E419">
         <v>2026</v>
@@ -8815,13 +8815,13 @@
         <v>0</v>
       </c>
       <c r="B420" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C420" t="s">
         <v>61</v>
       </c>
       <c r="D420">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E420">
         <v>2026</v>
@@ -8832,13 +8832,13 @@
         <v>0</v>
       </c>
       <c r="B421" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C421" t="s">
         <v>62</v>
       </c>
       <c r="D421">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E421">
         <v>2026</v>
@@ -8849,13 +8849,13 @@
         <v>0</v>
       </c>
       <c r="B422" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C422" t="s">
         <v>63</v>
       </c>
       <c r="D422">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="E422">
         <v>2026</v>
@@ -8866,13 +8866,13 @@
         <v>0</v>
       </c>
       <c r="B423" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C423" t="s">
         <v>64</v>
       </c>
       <c r="D423">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E423">
         <v>2026</v>
@@ -8883,13 +8883,13 @@
         <v>0</v>
       </c>
       <c r="B424" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C424" t="s">
         <v>65</v>
       </c>
       <c r="D424">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E424">
         <v>2026</v>
@@ -8900,13 +8900,13 @@
         <v>0</v>
       </c>
       <c r="B425" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C425" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D425">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E425">
         <v>2026</v>
@@ -8917,13 +8917,13 @@
         <v>0</v>
       </c>
       <c r="B426" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C426" t="s">
         <v>40</v>
       </c>
       <c r="D426">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E426">
         <v>2026</v>
@@ -8934,13 +8934,13 @@
         <v>0</v>
       </c>
       <c r="B427" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C427" t="s">
         <v>41</v>
       </c>
       <c r="D427">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E427">
         <v>2026</v>
@@ -8951,13 +8951,13 @@
         <v>0</v>
       </c>
       <c r="B428" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C428" t="s">
         <v>42</v>
       </c>
       <c r="D428">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E428">
         <v>2026</v>
@@ -8968,13 +8968,13 @@
         <v>0</v>
       </c>
       <c r="B429" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C429" t="s">
         <v>43</v>
       </c>
       <c r="D429">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E429">
         <v>2026</v>
@@ -8985,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="B430" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C430" t="s">
         <v>44</v>
@@ -9002,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="B431" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C431" t="s">
         <v>45</v>
@@ -9019,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="B432" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C432" t="s">
         <v>46</v>
@@ -9036,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="B433" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C433" t="s">
         <v>47</v>
@@ -9053,13 +9053,13 @@
         <v>0</v>
       </c>
       <c r="B434" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C434" t="s">
         <v>48</v>
       </c>
       <c r="D434">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E434">
         <v>2026</v>
@@ -9070,13 +9070,13 @@
         <v>0</v>
       </c>
       <c r="B435" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C435" t="s">
         <v>49</v>
       </c>
       <c r="D435">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E435">
         <v>2026</v>
@@ -9087,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="B436" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C436" t="s">
         <v>50</v>
@@ -9104,10 +9104,10 @@
         <v>0</v>
       </c>
       <c r="B437" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C437" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D437">
         <v>11</v>
@@ -9121,13 +9121,13 @@
         <v>0</v>
       </c>
       <c r="B438" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C438" t="s">
         <v>55</v>
       </c>
       <c r="D438">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E438">
         <v>2026</v>
@@ -9138,13 +9138,13 @@
         <v>0</v>
       </c>
       <c r="B439" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C439" t="s">
         <v>56</v>
       </c>
       <c r="D439">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E439">
         <v>2026</v>
@@ -9155,13 +9155,13 @@
         <v>0</v>
       </c>
       <c r="B440" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C440" t="s">
         <v>57</v>
       </c>
       <c r="D440">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E440">
         <v>2026</v>
@@ -9172,13 +9172,13 @@
         <v>0</v>
       </c>
       <c r="B441" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C441" t="s">
         <v>58</v>
       </c>
       <c r="D441">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E441">
         <v>2026</v>
@@ -9189,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="B442" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C442" t="s">
         <v>59</v>
@@ -9209,7 +9209,7 @@
         <v>189</v>
       </c>
       <c r="C443" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D443">
         <v>11</v>
@@ -9223,13 +9223,13 @@
         <v>0</v>
       </c>
       <c r="B444" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C444" t="s">
         <v>19</v>
       </c>
       <c r="D444">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E444">
         <v>2026</v>
@@ -9240,13 +9240,13 @@
         <v>0</v>
       </c>
       <c r="B445" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C445" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D445">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E445">
         <v>2026</v>
@@ -9257,13 +9257,7 @@
         <v>0</v>
       </c>
       <c r="B446" t="s">
-        <v>191</v>
-      </c>
-      <c r="C446" t="s">
-        <v>27</v>
-      </c>
-      <c r="D446">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="E446">
         <v>2026</v>
@@ -9274,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="B447" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E447">
         <v>2026</v>
@@ -9285,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="B448" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E448">
         <v>2026</v>
@@ -9296,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="B449" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E449">
         <v>2026</v>
@@ -9307,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="B450" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E450">
         <v>2026</v>
@@ -9318,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="B451" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E451">
         <v>2026</v>
@@ -9329,7 +9323,7 @@
         <v>0</v>
       </c>
       <c r="B452" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E452">
         <v>2026</v>
@@ -9340,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="B453" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E453">
         <v>2026</v>
@@ -9351,25 +9345,14 @@
         <v>0</v>
       </c>
       <c r="B454" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E454">
         <v>2026</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>0</v>
-      </c>
-      <c r="B455" t="s">
-        <v>192</v>
-      </c>
-      <c r="E455">
-        <v>2026</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F455" xr:uid="{9DD1486C-51B6-B749-A34B-52AA7241C016}"/>
+  <autoFilter ref="A1:F454" xr:uid="{9DD1486C-51B6-B749-A34B-52AA7241C016}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>